--- a/玉米大豆历史数据/玉米基差/Oregon Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Oregon Basis.xlsx
@@ -71,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -85,6 +85,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,8 +505,6 @@
       <c r="D2" t="n">
         <v>649</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,8 +525,6 @@
       <c r="D3" t="n">
         <v>201</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17342,7 +17339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:O203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17372,62 +17369,67 @@
           <t>Current</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Jan_Delivery</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Feb_Delivery</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mar_Delivery</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Apr_Delivery</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>May_Delivery</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jun_Delivery</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Jul_Delivery</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Aug_Delivery</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sep_Delivery</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Oct_Delivery</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Nov_Delivery</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Dec_Delivery</t>
         </is>
@@ -17440,7 +17442,6 @@
       <c r="B2" s="3" t="n">
         <v>226.5</v>
       </c>
-      <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
@@ -17452,6 +17453,7 @@
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -17460,7 +17462,6 @@
       <c r="B3" s="3" t="n">
         <v>226.5</v>
       </c>
-      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
@@ -17472,6 +17473,7 @@
       <c r="L3" s="4" t="n"/>
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -17480,7 +17482,6 @@
       <c r="B4" s="3" t="n">
         <v>216.5</v>
       </c>
-      <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
@@ -17492,6 +17493,7 @@
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
+      <c r="O4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -17500,7 +17502,6 @@
       <c r="B5" s="3" t="n">
         <v>212.5</v>
       </c>
-      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
@@ -17512,6 +17513,7 @@
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -17520,7 +17522,6 @@
       <c r="B6" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
@@ -17532,6 +17533,7 @@
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -17540,7 +17542,6 @@
       <c r="B7" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
@@ -17552,6 +17553,7 @@
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -17560,7 +17562,6 @@
       <c r="B8" s="3" t="n">
         <v>218.5</v>
       </c>
-      <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
@@ -17572,6 +17573,7 @@
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -17580,7 +17582,6 @@
       <c r="B9" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
@@ -17592,6 +17593,7 @@
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -17600,7 +17602,6 @@
       <c r="B10" s="3" t="n">
         <v>232.5</v>
       </c>
-      <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
@@ -17612,6 +17613,7 @@
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
       <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -17620,7 +17622,6 @@
       <c r="B11" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
@@ -17632,6 +17633,7 @@
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -17640,7 +17642,6 @@
       <c r="B12" s="3" t="n">
         <v>267</v>
       </c>
-      <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
@@ -17652,6 +17653,7 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -17660,7 +17662,6 @@
       <c r="B13" s="3" t="n">
         <v>309.5</v>
       </c>
-      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
@@ -17672,6 +17673,7 @@
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -17680,7 +17682,6 @@
       <c r="B14" s="3" t="n">
         <v>310</v>
       </c>
-      <c r="C14" s="4" t="n"/>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
@@ -17692,6 +17693,7 @@
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -17700,7 +17702,6 @@
       <c r="B15" s="3" t="n">
         <v>312.5</v>
       </c>
-      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
@@ -17712,6 +17713,7 @@
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -17720,7 +17722,6 @@
       <c r="B16" s="3" t="n">
         <v>310</v>
       </c>
-      <c r="C16" s="4" t="n"/>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
@@ -17732,6 +17733,7 @@
       <c r="L16" s="4" t="n"/>
       <c r="M16" s="4" t="n"/>
       <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -17740,7 +17742,6 @@
       <c r="B17" s="3" t="n">
         <v>310</v>
       </c>
-      <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
@@ -17752,6 +17753,7 @@
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
       <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -17760,7 +17762,6 @@
       <c r="B18" s="3" t="n">
         <v>307.5</v>
       </c>
-      <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
@@ -17772,6 +17773,7 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -17780,7 +17782,6 @@
       <c r="B19" s="3" t="n">
         <v>307.5</v>
       </c>
-      <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
@@ -17792,6 +17793,7 @@
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -17800,7 +17802,6 @@
       <c r="B20" s="3" t="n">
         <v>297.5</v>
       </c>
-      <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
@@ -17812,6 +17813,7 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -17820,7 +17822,6 @@
       <c r="B21" s="3" t="n">
         <v>285.5</v>
       </c>
-      <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
@@ -17832,6 +17833,7 @@
       <c r="L21" s="4" t="n"/>
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -17840,7 +17842,6 @@
       <c r="B22" s="3" t="n">
         <v>279</v>
       </c>
-      <c r="C22" s="4" t="n"/>
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
@@ -17852,6 +17853,7 @@
       <c r="L22" s="4" t="n"/>
       <c r="M22" s="4" t="n"/>
       <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -17860,7 +17862,6 @@
       <c r="B23" s="3" t="n">
         <v>287.5</v>
       </c>
-      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
@@ -17872,6 +17873,7 @@
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -17880,7 +17882,6 @@
       <c r="B24" s="3" t="n">
         <v>287.5</v>
       </c>
-      <c r="C24" s="4" t="n"/>
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
@@ -17892,6 +17893,7 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -17900,7 +17902,6 @@
       <c r="B25" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
@@ -17912,6 +17913,7 @@
       <c r="L25" s="4" t="n"/>
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -17920,7 +17922,6 @@
       <c r="B26" s="3" t="n">
         <v>297.5</v>
       </c>
-      <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
@@ -17932,6 +17933,7 @@
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
       <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -17940,7 +17942,6 @@
       <c r="B27" s="3" t="n">
         <v>276.5</v>
       </c>
-      <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
@@ -17952,6 +17953,7 @@
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
       <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -17960,7 +17962,6 @@
       <c r="B28" s="3" t="n">
         <v>266.5</v>
       </c>
-      <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
@@ -17972,6 +17973,7 @@
       <c r="L28" s="4" t="n"/>
       <c r="M28" s="4" t="n"/>
       <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -17980,7 +17982,6 @@
       <c r="B29" s="3" t="n">
         <v>266.5</v>
       </c>
-      <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
@@ -17992,6 +17993,7 @@
       <c r="L29" s="4" t="n"/>
       <c r="M29" s="4" t="n"/>
       <c r="N29" s="4" t="n"/>
+      <c r="O29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -18000,7 +18002,6 @@
       <c r="B30" s="3" t="n">
         <v>245.5</v>
       </c>
-      <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
@@ -18012,6 +18013,7 @@
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
       <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -18020,7 +18022,6 @@
       <c r="B31" s="3" t="n">
         <v>248.5</v>
       </c>
-      <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
@@ -18032,6 +18033,7 @@
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -18040,7 +18042,6 @@
       <c r="B32" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
@@ -18052,6 +18053,7 @@
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -18060,7 +18062,6 @@
       <c r="B33" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
@@ -18072,6 +18073,7 @@
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
       <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -18080,7 +18082,6 @@
       <c r="B34" s="3" t="n">
         <v>242.5</v>
       </c>
-      <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
@@ -18092,6 +18093,7 @@
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -18100,7 +18102,6 @@
       <c r="B35" s="3" t="n">
         <v>234.5</v>
       </c>
-      <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
@@ -18112,6 +18113,7 @@
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
       <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -18120,7 +18122,6 @@
       <c r="B36" s="3" t="n">
         <v>223.5</v>
       </c>
-      <c r="C36" s="4" t="n"/>
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
@@ -18132,6 +18133,7 @@
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -18140,7 +18142,6 @@
       <c r="B37" s="3" t="n">
         <v>225.5</v>
       </c>
-      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
@@ -18152,6 +18153,7 @@
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
+      <c r="O37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -18160,7 +18162,6 @@
       <c r="B38" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="C38" s="4" t="n"/>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
@@ -18172,6 +18173,7 @@
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -18180,7 +18182,6 @@
       <c r="B39" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
@@ -18192,6 +18193,7 @@
       <c r="L39" s="4" t="n"/>
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
+      <c r="O39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -18200,7 +18202,6 @@
       <c r="B40" s="3" t="n">
         <v>225.5</v>
       </c>
-      <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
@@ -18212,6 +18213,7 @@
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="n"/>
       <c r="N40" s="4" t="n"/>
+      <c r="O40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -18220,7 +18222,6 @@
       <c r="B41" s="3" t="n">
         <v>215</v>
       </c>
-      <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
@@ -18232,6 +18233,7 @@
       <c r="L41" s="4" t="n"/>
       <c r="M41" s="4" t="n"/>
       <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -18240,7 +18242,6 @@
       <c r="B42" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
@@ -18252,6 +18253,7 @@
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -18260,7 +18262,6 @@
       <c r="B43" s="3" t="n">
         <v>202.5</v>
       </c>
-      <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
@@ -18272,6 +18273,7 @@
       <c r="L43" s="4" t="n"/>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
+      <c r="O43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -18280,7 +18282,6 @@
       <c r="B44" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
@@ -18292,6 +18293,7 @@
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -18300,7 +18302,6 @@
       <c r="B45" s="3" t="n">
         <v>197.5</v>
       </c>
-      <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
@@ -18312,6 +18313,7 @@
       <c r="L45" s="4" t="n"/>
       <c r="M45" s="4" t="n"/>
       <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -18320,7 +18322,6 @@
       <c r="B46" s="3" t="n">
         <v>202.5</v>
       </c>
-      <c r="C46" s="4" t="n"/>
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
@@ -18332,6 +18333,7 @@
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="n"/>
       <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -18340,7 +18342,6 @@
       <c r="B47" s="3" t="n">
         <v>202.5</v>
       </c>
-      <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
@@ -18352,6 +18353,7 @@
       <c r="L47" s="4" t="n"/>
       <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -18360,7 +18362,6 @@
       <c r="B48" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C48" s="4" t="n"/>
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
@@ -18372,6 +18373,7 @@
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
+      <c r="O48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -18380,7 +18382,6 @@
       <c r="B49" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
@@ -18392,6 +18393,7 @@
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
       <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -18400,7 +18402,6 @@
       <c r="B50" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
@@ -18412,6 +18413,7 @@
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
       <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -18420,7 +18422,6 @@
       <c r="B51" s="3" t="n">
         <v>210</v>
       </c>
-      <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
@@ -18432,6 +18433,7 @@
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
       <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -18440,7 +18442,6 @@
       <c r="B52" s="3" t="n">
         <v>208.5</v>
       </c>
-      <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
@@ -18452,6 +18453,7 @@
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -18460,7 +18462,6 @@
       <c r="B53" s="3" t="n">
         <v>208.5</v>
       </c>
-      <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
@@ -18472,6 +18473,7 @@
       <c r="L53" s="4" t="n"/>
       <c r="M53" s="4" t="n"/>
       <c r="N53" s="4" t="n"/>
+      <c r="O53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -18480,7 +18482,6 @@
       <c r="B54" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C54" s="4" t="n"/>
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
@@ -18492,6 +18493,7 @@
       <c r="L54" s="4" t="n"/>
       <c r="M54" s="4" t="n"/>
       <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -18500,7 +18502,6 @@
       <c r="B55" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
@@ -18512,6 +18513,7 @@
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
       <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -18520,7 +18522,6 @@
       <c r="B56" s="3" t="n">
         <v>220.5</v>
       </c>
-      <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
@@ -18532,6 +18533,7 @@
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="4" t="n"/>
       <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -18540,7 +18542,6 @@
       <c r="B57" s="3" t="n">
         <v>222.5</v>
       </c>
-      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
@@ -18552,6 +18553,7 @@
       <c r="L57" s="4" t="n"/>
       <c r="M57" s="4" t="n"/>
       <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -18560,7 +18562,6 @@
       <c r="B58" s="3" t="n">
         <v>222.5</v>
       </c>
-      <c r="C58" s="4" t="n"/>
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
@@ -18572,6 +18573,7 @@
       <c r="L58" s="4" t="n"/>
       <c r="M58" s="4" t="n"/>
       <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -18580,7 +18582,6 @@
       <c r="B59" s="3" t="n">
         <v>222.5</v>
       </c>
-      <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
@@ -18592,6 +18593,7 @@
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
       <c r="N59" s="4" t="n"/>
+      <c r="O59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -18600,7 +18602,6 @@
       <c r="B60" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C60" s="4" t="n"/>
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
@@ -18612,6 +18613,7 @@
       <c r="L60" s="4" t="n"/>
       <c r="M60" s="4" t="n"/>
       <c r="N60" s="4" t="n"/>
+      <c r="O60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -18620,7 +18622,6 @@
       <c r="B61" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
@@ -18632,6 +18633,7 @@
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
       <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -18640,7 +18642,6 @@
       <c r="B62" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C62" s="4" t="n"/>
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
@@ -18652,6 +18653,7 @@
       <c r="L62" s="4" t="n"/>
       <c r="M62" s="4" t="n"/>
       <c r="N62" s="4" t="n"/>
+      <c r="O62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -18660,7 +18662,6 @@
       <c r="B63" s="3" t="n">
         <v>229.5</v>
       </c>
-      <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
@@ -18672,6 +18673,7 @@
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n"/>
+      <c r="O63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -18680,7 +18682,6 @@
       <c r="B64" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
@@ -18692,6 +18693,7 @@
       <c r="L64" s="4" t="n"/>
       <c r="M64" s="4" t="n"/>
       <c r="N64" s="4" t="n"/>
+      <c r="O64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -18700,7 +18702,6 @@
       <c r="B65" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
@@ -18712,6 +18713,7 @@
       <c r="L65" s="4" t="n"/>
       <c r="M65" s="4" t="n"/>
       <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -18720,7 +18722,6 @@
       <c r="B66" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C66" s="4" t="n"/>
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
@@ -18732,6 +18733,7 @@
       <c r="L66" s="4" t="n"/>
       <c r="M66" s="4" t="n"/>
       <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -18740,7 +18742,6 @@
       <c r="B67" s="3" t="n">
         <v>228.5</v>
       </c>
-      <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
@@ -18752,6 +18753,7 @@
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -18760,7 +18762,6 @@
       <c r="B68" s="3" t="n">
         <v>231</v>
       </c>
-      <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
@@ -18772,6 +18773,7 @@
       <c r="L68" s="4" t="n"/>
       <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
+      <c r="O68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -18780,7 +18782,6 @@
       <c r="B69" s="3" t="n">
         <v>231</v>
       </c>
-      <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
@@ -18792,6 +18793,7 @@
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="n"/>
       <c r="N69" s="4" t="n"/>
+      <c r="O69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -18800,7 +18802,6 @@
       <c r="B70" s="3" t="n">
         <v>234.5</v>
       </c>
-      <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
@@ -18812,6 +18813,7 @@
       <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="n"/>
       <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -18820,7 +18822,6 @@
       <c r="B71" s="3" t="n">
         <v>235.5</v>
       </c>
-      <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
@@ -18832,6 +18833,7 @@
       <c r="L71" s="4" t="n"/>
       <c r="M71" s="4" t="n"/>
       <c r="N71" s="4" t="n"/>
+      <c r="O71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -18840,7 +18842,6 @@
       <c r="B72" s="3" t="n">
         <v>229.5</v>
       </c>
-      <c r="C72" s="4" t="n"/>
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
@@ -18852,6 +18853,7 @@
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
       <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -18860,7 +18862,6 @@
       <c r="B73" s="3" t="n">
         <v>229.5</v>
       </c>
-      <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
@@ -18872,6 +18873,7 @@
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
       <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -18880,7 +18882,6 @@
       <c r="B74" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
@@ -18892,6 +18893,7 @@
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -18900,7 +18902,6 @@
       <c r="B75" s="3" t="n">
         <v>218</v>
       </c>
-      <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
@@ -18912,6 +18913,7 @@
       <c r="L75" s="4" t="n"/>
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="n"/>
+      <c r="O75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -18920,7 +18922,6 @@
       <c r="B76" s="3" t="n">
         <v>201.5</v>
       </c>
-      <c r="C76" s="4" t="n"/>
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
@@ -18932,6 +18933,7 @@
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
       <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -18940,7 +18942,6 @@
       <c r="B77" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="C77" s="4" t="n"/>
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
@@ -18952,6 +18953,7 @@
       <c r="L77" s="4" t="n"/>
       <c r="M77" s="4" t="n"/>
       <c r="N77" s="4" t="n"/>
+      <c r="O77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -18960,7 +18962,6 @@
       <c r="B78" s="3" t="n">
         <v>198.5</v>
       </c>
-      <c r="C78" s="4" t="n"/>
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
@@ -18972,6 +18973,7 @@
       <c r="L78" s="4" t="n"/>
       <c r="M78" s="4" t="n"/>
       <c r="N78" s="4" t="n"/>
+      <c r="O78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -18980,7 +18982,6 @@
       <c r="B79" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="C79" s="4" t="n"/>
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
@@ -18992,6 +18993,7 @@
       <c r="L79" s="4" t="n"/>
       <c r="M79" s="4" t="n"/>
       <c r="N79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -19000,7 +19002,6 @@
       <c r="B80" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="C80" s="4" t="n"/>
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
@@ -19012,6 +19013,7 @@
       <c r="L80" s="4" t="n"/>
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
+      <c r="O80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -19020,7 +19022,6 @@
       <c r="B81" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
@@ -19032,6 +19033,7 @@
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n"/>
       <c r="N81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -19040,7 +19042,6 @@
       <c r="B82" s="3" t="n">
         <v>181</v>
       </c>
-      <c r="C82" s="4" t="n"/>
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
@@ -19052,6 +19053,7 @@
       <c r="L82" s="4" t="n"/>
       <c r="M82" s="4" t="n"/>
       <c r="N82" s="4" t="n"/>
+      <c r="O82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -19060,7 +19062,6 @@
       <c r="B83" s="3" t="n">
         <v>178.5</v>
       </c>
-      <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
@@ -19072,6 +19073,7 @@
       <c r="L83" s="4" t="n"/>
       <c r="M83" s="4" t="n"/>
       <c r="N83" s="4" t="n"/>
+      <c r="O83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -19080,7 +19082,6 @@
       <c r="B84" s="3" t="n">
         <v>183.5</v>
       </c>
-      <c r="C84" s="4" t="n"/>
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
@@ -19092,6 +19093,7 @@
       <c r="L84" s="4" t="n"/>
       <c r="M84" s="4" t="n"/>
       <c r="N84" s="4" t="n"/>
+      <c r="O84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -19100,7 +19102,6 @@
       <c r="B85" s="3" t="n">
         <v>186</v>
       </c>
-      <c r="C85" s="4" t="n"/>
       <c r="D85" s="4" t="n"/>
       <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="n"/>
@@ -19112,6 +19113,7 @@
       <c r="L85" s="4" t="n"/>
       <c r="M85" s="4" t="n"/>
       <c r="N85" s="4" t="n"/>
+      <c r="O85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -19120,7 +19122,6 @@
       <c r="B86" s="3" t="n">
         <v>180.5</v>
       </c>
-      <c r="C86" s="4" t="n"/>
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
@@ -19132,6 +19133,7 @@
       <c r="L86" s="4" t="n"/>
       <c r="M86" s="4" t="n"/>
       <c r="N86" s="4" t="n"/>
+      <c r="O86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -19140,7 +19142,6 @@
       <c r="B87" s="3" t="n">
         <v>180.5</v>
       </c>
-      <c r="C87" s="4" t="n"/>
       <c r="D87" s="4" t="n"/>
       <c r="E87" s="4" t="n"/>
       <c r="F87" s="4" t="n"/>
@@ -19152,6 +19153,7 @@
       <c r="L87" s="4" t="n"/>
       <c r="M87" s="4" t="n"/>
       <c r="N87" s="4" t="n"/>
+      <c r="O87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -19160,7 +19162,6 @@
       <c r="B88" s="3" t="n">
         <v>184.5</v>
       </c>
-      <c r="C88" s="4" t="n"/>
       <c r="D88" s="4" t="n"/>
       <c r="E88" s="4" t="n"/>
       <c r="F88" s="4" t="n"/>
@@ -19172,6 +19173,7 @@
       <c r="L88" s="4" t="n"/>
       <c r="M88" s="4" t="n"/>
       <c r="N88" s="4" t="n"/>
+      <c r="O88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -19180,7 +19182,6 @@
       <c r="B89" s="3" t="n">
         <v>187.5</v>
       </c>
-      <c r="C89" s="4" t="n"/>
       <c r="D89" s="4" t="n"/>
       <c r="E89" s="4" t="n"/>
       <c r="F89" s="4" t="n"/>
@@ -19192,6 +19193,7 @@
       <c r="L89" s="4" t="n"/>
       <c r="M89" s="4" t="n"/>
       <c r="N89" s="4" t="n"/>
+      <c r="O89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -19200,7 +19202,6 @@
       <c r="B90" s="3" t="n">
         <v>187.5</v>
       </c>
-      <c r="C90" s="4" t="n"/>
       <c r="D90" s="4" t="n"/>
       <c r="E90" s="4" t="n"/>
       <c r="F90" s="4" t="n"/>
@@ -19212,6 +19213,7 @@
       <c r="L90" s="4" t="n"/>
       <c r="M90" s="4" t="n"/>
       <c r="N90" s="4" t="n"/>
+      <c r="O90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -19220,7 +19222,6 @@
       <c r="B91" s="3" t="n">
         <v>189</v>
       </c>
-      <c r="C91" s="4" t="n"/>
       <c r="D91" s="4" t="n"/>
       <c r="E91" s="4" t="n"/>
       <c r="F91" s="4" t="n"/>
@@ -19232,6 +19233,7 @@
       <c r="L91" s="4" t="n"/>
       <c r="M91" s="4" t="n"/>
       <c r="N91" s="4" t="n"/>
+      <c r="O91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -19240,7 +19242,6 @@
       <c r="B92" s="3" t="n">
         <v>193.5</v>
       </c>
-      <c r="C92" s="4" t="n"/>
       <c r="D92" s="4" t="n"/>
       <c r="E92" s="4" t="n"/>
       <c r="F92" s="4" t="n"/>
@@ -19252,6 +19253,7 @@
       <c r="L92" s="4" t="n"/>
       <c r="M92" s="4" t="n"/>
       <c r="N92" s="4" t="n"/>
+      <c r="O92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -19260,7 +19262,6 @@
       <c r="B93" s="3" t="n">
         <v>192.5</v>
       </c>
-      <c r="C93" s="4" t="n"/>
       <c r="D93" s="4" t="n"/>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="n"/>
@@ -19272,6 +19273,7 @@
       <c r="L93" s="4" t="n"/>
       <c r="M93" s="4" t="n"/>
       <c r="N93" s="4" t="n"/>
+      <c r="O93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -19280,7 +19282,6 @@
       <c r="B94" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="C94" s="4" t="n"/>
       <c r="D94" s="4" t="n"/>
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
@@ -19292,6 +19293,7 @@
       <c r="L94" s="4" t="n"/>
       <c r="M94" s="4" t="n"/>
       <c r="N94" s="4" t="n"/>
+      <c r="O94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -19300,7 +19302,6 @@
       <c r="B95" s="3" t="n">
         <v>180.5</v>
       </c>
-      <c r="C95" s="4" t="n"/>
       <c r="D95" s="4" t="n"/>
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="n"/>
@@ -19312,6 +19313,7 @@
       <c r="L95" s="4" t="n"/>
       <c r="M95" s="4" t="n"/>
       <c r="N95" s="4" t="n"/>
+      <c r="O95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -19320,7 +19322,6 @@
       <c r="B96" s="3" t="n">
         <v>186</v>
       </c>
-      <c r="C96" s="4" t="n"/>
       <c r="D96" s="4" t="n"/>
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="n"/>
@@ -19332,6 +19333,7 @@
       <c r="L96" s="4" t="n"/>
       <c r="M96" s="4" t="n"/>
       <c r="N96" s="4" t="n"/>
+      <c r="O96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -19340,7 +19342,6 @@
       <c r="B97" s="3" t="n">
         <v>181</v>
       </c>
-      <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="n"/>
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="n"/>
@@ -19352,6 +19353,7 @@
       <c r="L97" s="4" t="n"/>
       <c r="M97" s="4" t="n"/>
       <c r="N97" s="4" t="n"/>
+      <c r="O97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -19360,7 +19362,6 @@
       <c r="B98" s="3" t="n">
         <v>182.5</v>
       </c>
-      <c r="C98" s="4" t="n"/>
       <c r="D98" s="4" t="n"/>
       <c r="E98" s="4" t="n"/>
       <c r="F98" s="4" t="n"/>
@@ -19372,6 +19373,7 @@
       <c r="L98" s="4" t="n"/>
       <c r="M98" s="4" t="n"/>
       <c r="N98" s="4" t="n"/>
+      <c r="O98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -19380,7 +19382,6 @@
       <c r="B99" s="3" t="n">
         <v>185.5</v>
       </c>
-      <c r="C99" s="4" t="n"/>
       <c r="D99" s="4" t="n"/>
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="n"/>
@@ -19392,6 +19393,7 @@
       <c r="L99" s="4" t="n"/>
       <c r="M99" s="4" t="n"/>
       <c r="N99" s="4" t="n"/>
+      <c r="O99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -19400,7 +19402,6 @@
       <c r="B100" s="3" t="n">
         <v>187.5</v>
       </c>
-      <c r="C100" s="4" t="n"/>
       <c r="D100" s="4" t="n"/>
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
@@ -19412,6 +19413,7 @@
       <c r="L100" s="4" t="n"/>
       <c r="M100" s="4" t="n"/>
       <c r="N100" s="4" t="n"/>
+      <c r="O100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -19420,7 +19422,6 @@
       <c r="B101" s="3" t="n">
         <v>182</v>
       </c>
-      <c r="C101" s="4" t="n"/>
       <c r="D101" s="4" t="n"/>
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
@@ -19432,6 +19433,7 @@
       <c r="L101" s="4" t="n"/>
       <c r="M101" s="4" t="n"/>
       <c r="N101" s="4" t="n"/>
+      <c r="O101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -19440,7 +19442,6 @@
       <c r="B102" s="3" t="n">
         <v>182</v>
       </c>
-      <c r="C102" s="4" t="n"/>
       <c r="D102" s="4" t="n"/>
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
@@ -19452,6 +19453,7 @@
       <c r="L102" s="4" t="n"/>
       <c r="M102" s="4" t="n"/>
       <c r="N102" s="4" t="n"/>
+      <c r="O102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -19460,7 +19462,6 @@
       <c r="B103" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="C103" s="4" t="n"/>
       <c r="D103" s="4" t="n"/>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
@@ -19472,6 +19473,7 @@
       <c r="L103" s="4" t="n"/>
       <c r="M103" s="4" t="n"/>
       <c r="N103" s="4" t="n"/>
+      <c r="O103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -19480,7 +19482,6 @@
       <c r="B104" s="3" t="n">
         <v>189</v>
       </c>
-      <c r="C104" s="4" t="n"/>
       <c r="D104" s="4" t="n"/>
       <c r="E104" s="4" t="n"/>
       <c r="F104" s="4" t="n"/>
@@ -19492,6 +19493,7 @@
       <c r="L104" s="4" t="n"/>
       <c r="M104" s="4" t="n"/>
       <c r="N104" s="4" t="n"/>
+      <c r="O104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -19500,7 +19502,6 @@
       <c r="B105" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="C105" s="4" t="n"/>
       <c r="D105" s="4" t="n"/>
       <c r="E105" s="4" t="n"/>
       <c r="F105" s="4" t="n"/>
@@ -19512,6 +19513,7 @@
       <c r="L105" s="4" t="n"/>
       <c r="M105" s="4" t="n"/>
       <c r="N105" s="4" t="n"/>
+      <c r="O105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -19520,7 +19522,6 @@
       <c r="B106" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="C106" s="4" t="n"/>
       <c r="D106" s="4" t="n"/>
       <c r="E106" s="4" t="n"/>
       <c r="F106" s="4" t="n"/>
@@ -19532,6 +19533,7 @@
       <c r="L106" s="4" t="n"/>
       <c r="M106" s="4" t="n"/>
       <c r="N106" s="4" t="n"/>
+      <c r="O106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -19540,7 +19542,6 @@
       <c r="B107" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="C107" s="4" t="n"/>
       <c r="D107" s="4" t="n"/>
       <c r="E107" s="4" t="n"/>
       <c r="F107" s="4" t="n"/>
@@ -19552,6 +19553,7 @@
       <c r="L107" s="4" t="n"/>
       <c r="M107" s="4" t="n"/>
       <c r="N107" s="4" t="n"/>
+      <c r="O107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -19560,7 +19562,6 @@
       <c r="B108" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="C108" s="4" t="n"/>
       <c r="D108" s="4" t="n"/>
       <c r="E108" s="4" t="n"/>
       <c r="F108" s="4" t="n"/>
@@ -19572,6 +19573,7 @@
       <c r="L108" s="4" t="n"/>
       <c r="M108" s="4" t="n"/>
       <c r="N108" s="4" t="n"/>
+      <c r="O108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -19580,7 +19582,6 @@
       <c r="B109" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="C109" s="4" t="n"/>
       <c r="D109" s="4" t="n"/>
       <c r="E109" s="4" t="n"/>
       <c r="F109" s="4" t="n"/>
@@ -19592,6 +19593,7 @@
       <c r="L109" s="4" t="n"/>
       <c r="M109" s="4" t="n"/>
       <c r="N109" s="4" t="n"/>
+      <c r="O109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -19600,7 +19602,6 @@
       <c r="B110" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="C110" s="4" t="n"/>
       <c r="D110" s="4" t="n"/>
       <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="n"/>
@@ -19612,6 +19613,7 @@
       <c r="L110" s="4" t="n"/>
       <c r="M110" s="4" t="n"/>
       <c r="N110" s="4" t="n"/>
+      <c r="O110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -19620,7 +19622,6 @@
       <c r="B111" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="C111" s="4" t="n"/>
       <c r="D111" s="4" t="n"/>
       <c r="E111" s="4" t="n"/>
       <c r="F111" s="4" t="n"/>
@@ -19632,6 +19633,7 @@
       <c r="L111" s="4" t="n"/>
       <c r="M111" s="4" t="n"/>
       <c r="N111" s="4" t="n"/>
+      <c r="O111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -19640,7 +19642,6 @@
       <c r="B112" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="C112" s="4" t="n"/>
       <c r="D112" s="4" t="n"/>
       <c r="E112" s="4" t="n"/>
       <c r="F112" s="4" t="n"/>
@@ -19652,6 +19653,7 @@
       <c r="L112" s="4" t="n"/>
       <c r="M112" s="4" t="n"/>
       <c r="N112" s="4" t="n"/>
+      <c r="O112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -19660,7 +19662,6 @@
       <c r="B113" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="C113" s="4" t="n"/>
       <c r="D113" s="4" t="n"/>
       <c r="E113" s="4" t="n"/>
       <c r="F113" s="4" t="n"/>
@@ -19672,6 +19673,7 @@
       <c r="L113" s="4" t="n"/>
       <c r="M113" s="4" t="n"/>
       <c r="N113" s="4" t="n"/>
+      <c r="O113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -19680,7 +19682,6 @@
       <c r="B114" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="C114" s="4" t="n"/>
       <c r="D114" s="4" t="n"/>
       <c r="E114" s="4" t="n"/>
       <c r="F114" s="4" t="n"/>
@@ -19692,6 +19693,7 @@
       <c r="L114" s="4" t="n"/>
       <c r="M114" s="4" t="n"/>
       <c r="N114" s="4" t="n"/>
+      <c r="O114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -19700,7 +19702,6 @@
       <c r="B115" s="3" t="n">
         <v>179</v>
       </c>
-      <c r="C115" s="4" t="n"/>
       <c r="D115" s="4" t="n"/>
       <c r="E115" s="4" t="n"/>
       <c r="F115" s="4" t="n"/>
@@ -19712,6 +19713,7 @@
       <c r="L115" s="4" t="n"/>
       <c r="M115" s="4" t="n"/>
       <c r="N115" s="4" t="n"/>
+      <c r="O115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -19720,7 +19722,6 @@
       <c r="B116" s="3" t="n">
         <v>176.5</v>
       </c>
-      <c r="C116" s="4" t="n"/>
       <c r="D116" s="4" t="n"/>
       <c r="E116" s="4" t="n"/>
       <c r="F116" s="4" t="n"/>
@@ -19732,6 +19733,7 @@
       <c r="L116" s="4" t="n"/>
       <c r="M116" s="4" t="n"/>
       <c r="N116" s="4" t="n"/>
+      <c r="O116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -19740,7 +19742,6 @@
       <c r="B117" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="C117" s="4" t="n"/>
       <c r="D117" s="4" t="n"/>
       <c r="E117" s="4" t="n"/>
       <c r="F117" s="4" t="n"/>
@@ -19752,6 +19753,7 @@
       <c r="L117" s="4" t="n"/>
       <c r="M117" s="4" t="n"/>
       <c r="N117" s="4" t="n"/>
+      <c r="O117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -19760,7 +19762,6 @@
       <c r="B118" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="C118" s="4" t="n"/>
       <c r="D118" s="4" t="n"/>
       <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="n"/>
@@ -19772,6 +19773,7 @@
       <c r="L118" s="4" t="n"/>
       <c r="M118" s="4" t="n"/>
       <c r="N118" s="4" t="n"/>
+      <c r="O118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -19780,7 +19782,6 @@
       <c r="B119" s="3" t="n">
         <v>167.5</v>
       </c>
-      <c r="C119" s="4" t="n"/>
       <c r="D119" s="4" t="n"/>
       <c r="E119" s="4" t="n"/>
       <c r="F119" s="4" t="n"/>
@@ -19792,6 +19793,7 @@
       <c r="L119" s="4" t="n"/>
       <c r="M119" s="4" t="n"/>
       <c r="N119" s="4" t="n"/>
+      <c r="O119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -19800,7 +19802,6 @@
       <c r="B120" s="3" t="n">
         <v>170.5</v>
       </c>
-      <c r="C120" s="4" t="n"/>
       <c r="D120" s="4" t="n"/>
       <c r="E120" s="4" t="n"/>
       <c r="F120" s="4" t="n"/>
@@ -19812,6 +19813,7 @@
       <c r="L120" s="4" t="n"/>
       <c r="M120" s="4" t="n"/>
       <c r="N120" s="4" t="n"/>
+      <c r="O120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -19820,7 +19822,6 @@
       <c r="B121" s="3" t="n">
         <v>179</v>
       </c>
-      <c r="C121" s="4" t="n"/>
       <c r="D121" s="4" t="n"/>
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
@@ -19832,6 +19833,7 @@
       <c r="L121" s="4" t="n"/>
       <c r="M121" s="4" t="n"/>
       <c r="N121" s="4" t="n"/>
+      <c r="O121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -19840,7 +19842,6 @@
       <c r="B122" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="C122" s="4" t="n"/>
       <c r="D122" s="4" t="n"/>
       <c r="E122" s="4" t="n"/>
       <c r="F122" s="4" t="n"/>
@@ -19852,6 +19853,7 @@
       <c r="L122" s="4" t="n"/>
       <c r="M122" s="4" t="n"/>
       <c r="N122" s="4" t="n"/>
+      <c r="O122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -19860,7 +19862,6 @@
       <c r="B123" s="3" t="n">
         <v>172</v>
       </c>
-      <c r="C123" s="4" t="n"/>
       <c r="D123" s="4" t="n"/>
       <c r="E123" s="4" t="n"/>
       <c r="F123" s="4" t="n"/>
@@ -19872,6 +19873,7 @@
       <c r="L123" s="4" t="n"/>
       <c r="M123" s="4" t="n"/>
       <c r="N123" s="4" t="n"/>
+      <c r="O123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -19880,7 +19882,6 @@
       <c r="B124" s="3" t="n">
         <v>169.5</v>
       </c>
-      <c r="C124" s="4" t="n"/>
       <c r="D124" s="4" t="n"/>
       <c r="E124" s="4" t="n"/>
       <c r="F124" s="4" t="n"/>
@@ -19892,6 +19893,7 @@
       <c r="L124" s="4" t="n"/>
       <c r="M124" s="4" t="n"/>
       <c r="N124" s="4" t="n"/>
+      <c r="O124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -19900,7 +19902,6 @@
       <c r="B125" s="3" t="n">
         <v>164.5</v>
       </c>
-      <c r="C125" s="4" t="n"/>
       <c r="D125" s="4" t="n"/>
       <c r="E125" s="4" t="n"/>
       <c r="F125" s="4" t="n"/>
@@ -19912,6 +19913,7 @@
       <c r="L125" s="4" t="n"/>
       <c r="M125" s="4" t="n"/>
       <c r="N125" s="4" t="n"/>
+      <c r="O125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -19920,7 +19922,6 @@
       <c r="B126" s="3" t="n">
         <v>165.5</v>
       </c>
-      <c r="C126" s="4" t="n"/>
       <c r="D126" s="4" t="n"/>
       <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="n"/>
@@ -19932,6 +19933,7 @@
       <c r="L126" s="4" t="n"/>
       <c r="M126" s="4" t="n"/>
       <c r="N126" s="4" t="n"/>
+      <c r="O126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -19940,7 +19942,6 @@
       <c r="B127" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="C127" s="4" t="n"/>
       <c r="D127" s="4" t="n"/>
       <c r="E127" s="4" t="n"/>
       <c r="F127" s="4" t="n"/>
@@ -19952,6 +19953,7 @@
       <c r="L127" s="4" t="n"/>
       <c r="M127" s="4" t="n"/>
       <c r="N127" s="4" t="n"/>
+      <c r="O127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -19960,7 +19962,6 @@
       <c r="B128" s="3" t="n">
         <v>153.5</v>
       </c>
-      <c r="C128" s="4" t="n"/>
       <c r="D128" s="4" t="n"/>
       <c r="E128" s="4" t="n"/>
       <c r="F128" s="4" t="n"/>
@@ -19972,6 +19973,7 @@
       <c r="L128" s="4" t="n"/>
       <c r="M128" s="4" t="n"/>
       <c r="N128" s="4" t="n"/>
+      <c r="O128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -19980,7 +19982,6 @@
       <c r="B129" s="3" t="n">
         <v>152.5</v>
       </c>
-      <c r="C129" s="4" t="n"/>
       <c r="D129" s="4" t="n"/>
       <c r="E129" s="4" t="n"/>
       <c r="F129" s="4" t="n"/>
@@ -19992,6 +19993,7 @@
       <c r="L129" s="4" t="n"/>
       <c r="M129" s="4" t="n"/>
       <c r="N129" s="4" t="n"/>
+      <c r="O129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -20000,7 +20002,6 @@
       <c r="B130" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C130" s="4" t="n"/>
       <c r="D130" s="4" t="n"/>
       <c r="E130" s="4" t="n"/>
       <c r="F130" s="4" t="n"/>
@@ -20012,6 +20013,7 @@
       <c r="L130" s="4" t="n"/>
       <c r="M130" s="4" t="n"/>
       <c r="N130" s="4" t="n"/>
+      <c r="O130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -20020,7 +20022,6 @@
       <c r="B131" s="3" t="n">
         <v>154.5</v>
       </c>
-      <c r="C131" s="4" t="n"/>
       <c r="D131" s="4" t="n"/>
       <c r="E131" s="4" t="n"/>
       <c r="F131" s="4" t="n"/>
@@ -20032,6 +20033,7 @@
       <c r="L131" s="4" t="n"/>
       <c r="M131" s="4" t="n"/>
       <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -20040,7 +20042,6 @@
       <c r="B132" s="3" t="n">
         <v>153.5</v>
       </c>
-      <c r="C132" s="4" t="n"/>
       <c r="D132" s="4" t="n"/>
       <c r="E132" s="4" t="n"/>
       <c r="F132" s="4" t="n"/>
@@ -20052,6 +20053,7 @@
       <c r="L132" s="4" t="n"/>
       <c r="M132" s="4" t="n"/>
       <c r="N132" s="4" t="n"/>
+      <c r="O132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -20060,7 +20062,6 @@
       <c r="B133" s="3" t="n">
         <v>151.5</v>
       </c>
-      <c r="C133" s="4" t="n"/>
       <c r="D133" s="4" t="n"/>
       <c r="E133" s="4" t="n"/>
       <c r="F133" s="4" t="n"/>
@@ -20072,6 +20073,7 @@
       <c r="L133" s="4" t="n"/>
       <c r="M133" s="4" t="n"/>
       <c r="N133" s="4" t="n"/>
+      <c r="O133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -20080,7 +20082,6 @@
       <c r="B134" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="C134" s="4" t="n"/>
       <c r="D134" s="4" t="n"/>
       <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="n"/>
@@ -20092,6 +20093,7 @@
       <c r="L134" s="4" t="n"/>
       <c r="M134" s="4" t="n"/>
       <c r="N134" s="4" t="n"/>
+      <c r="O134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -20100,7 +20102,6 @@
       <c r="B135" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C135" s="4" t="n"/>
       <c r="D135" s="4" t="n"/>
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="n"/>
@@ -20112,6 +20113,7 @@
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
+      <c r="O135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -20120,7 +20122,6 @@
       <c r="B136" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="n"/>
       <c r="E136" s="4" t="n"/>
       <c r="F136" s="4" t="n"/>
@@ -20132,6 +20133,7 @@
       <c r="L136" s="4" t="n"/>
       <c r="M136" s="4" t="n"/>
       <c r="N136" s="4" t="n"/>
+      <c r="O136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -20140,7 +20142,6 @@
       <c r="B137" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="n"/>
       <c r="E137" s="4" t="n"/>
       <c r="F137" s="4" t="n"/>
@@ -20152,6 +20153,7 @@
       <c r="L137" s="4" t="n"/>
       <c r="M137" s="4" t="n"/>
       <c r="N137" s="4" t="n"/>
+      <c r="O137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -20160,7 +20162,6 @@
       <c r="B138" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="n"/>
       <c r="E138" s="4" t="n"/>
       <c r="F138" s="4" t="n"/>
@@ -20172,6 +20173,7 @@
       <c r="L138" s="4" t="n"/>
       <c r="M138" s="4" t="n"/>
       <c r="N138" s="4" t="n"/>
+      <c r="O138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -20180,7 +20182,6 @@
       <c r="B139" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C139" s="4" t="n"/>
       <c r="D139" s="4" t="n"/>
       <c r="E139" s="4" t="n"/>
       <c r="F139" s="4" t="n"/>
@@ -20192,6 +20193,7 @@
       <c r="L139" s="4" t="n"/>
       <c r="M139" s="4" t="n"/>
       <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -20200,7 +20202,6 @@
       <c r="B140" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C140" s="4" t="n"/>
       <c r="D140" s="4" t="n"/>
       <c r="E140" s="4" t="n"/>
       <c r="F140" s="4" t="n"/>
@@ -20212,6 +20213,7 @@
       <c r="L140" s="4" t="n"/>
       <c r="M140" s="4" t="n"/>
       <c r="N140" s="4" t="n"/>
+      <c r="O140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -20220,7 +20222,6 @@
       <c r="B141" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C141" s="4" t="n"/>
       <c r="D141" s="4" t="n"/>
       <c r="E141" s="4" t="n"/>
       <c r="F141" s="4" t="n"/>
@@ -20232,6 +20233,7 @@
       <c r="L141" s="4" t="n"/>
       <c r="M141" s="4" t="n"/>
       <c r="N141" s="4" t="n"/>
+      <c r="O141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -20240,7 +20242,6 @@
       <c r="B142" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C142" s="4" t="n"/>
       <c r="D142" s="4" t="n"/>
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="n"/>
@@ -20252,6 +20253,7 @@
       <c r="L142" s="4" t="n"/>
       <c r="M142" s="4" t="n"/>
       <c r="N142" s="4" t="n"/>
+      <c r="O142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -20260,7 +20262,6 @@
       <c r="B143" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C143" s="4" t="n"/>
       <c r="D143" s="4" t="n"/>
       <c r="E143" s="4" t="n"/>
       <c r="F143" s="4" t="n"/>
@@ -20272,6 +20273,7 @@
       <c r="L143" s="4" t="n"/>
       <c r="M143" s="4" t="n"/>
       <c r="N143" s="4" t="n"/>
+      <c r="O143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -20280,7 +20282,6 @@
       <c r="B144" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C144" s="4" t="n"/>
       <c r="D144" s="4" t="n"/>
       <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="n"/>
@@ -20292,6 +20293,7 @@
       <c r="L144" s="4" t="n"/>
       <c r="M144" s="4" t="n"/>
       <c r="N144" s="4" t="n"/>
+      <c r="O144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -20300,7 +20302,6 @@
       <c r="B145" s="3" t="n">
         <v>150.5</v>
       </c>
-      <c r="C145" s="4" t="n"/>
       <c r="D145" s="4" t="n"/>
       <c r="E145" s="4" t="n"/>
       <c r="F145" s="4" t="n"/>
@@ -20312,6 +20313,7 @@
       <c r="L145" s="4" t="n"/>
       <c r="M145" s="4" t="n"/>
       <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -20320,7 +20322,6 @@
       <c r="B146" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C146" s="4" t="n"/>
       <c r="D146" s="4" t="n"/>
       <c r="E146" s="4" t="n"/>
       <c r="F146" s="4" t="n"/>
@@ -20332,6 +20333,7 @@
       <c r="L146" s="4" t="n"/>
       <c r="M146" s="4" t="n"/>
       <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -20340,7 +20342,6 @@
       <c r="B147" s="3" t="n">
         <v>147.5</v>
       </c>
-      <c r="C147" s="4" t="n"/>
       <c r="D147" s="4" t="n"/>
       <c r="E147" s="4" t="n"/>
       <c r="F147" s="4" t="n"/>
@@ -20352,6 +20353,7 @@
       <c r="L147" s="4" t="n"/>
       <c r="M147" s="4" t="n"/>
       <c r="N147" s="4" t="n"/>
+      <c r="O147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -20360,7 +20362,6 @@
       <c r="B148" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C148" s="4" t="n"/>
       <c r="D148" s="4" t="n"/>
       <c r="E148" s="4" t="n"/>
       <c r="F148" s="4" t="n"/>
@@ -20372,6 +20373,7 @@
       <c r="L148" s="4" t="n"/>
       <c r="M148" s="4" t="n"/>
       <c r="N148" s="4" t="n"/>
+      <c r="O148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -20380,7 +20382,6 @@
       <c r="B149" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C149" s="4" t="n"/>
       <c r="D149" s="4" t="n"/>
       <c r="E149" s="4" t="n"/>
       <c r="F149" s="4" t="n"/>
@@ -20392,6 +20393,7 @@
       <c r="L149" s="4" t="n"/>
       <c r="M149" s="4" t="n"/>
       <c r="N149" s="4" t="n"/>
+      <c r="O149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -20400,7 +20402,6 @@
       <c r="B150" s="3" t="n">
         <v>143.5</v>
       </c>
-      <c r="C150" s="4" t="n"/>
       <c r="D150" s="4" t="n"/>
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="n"/>
@@ -20412,6 +20413,7 @@
       <c r="L150" s="4" t="n"/>
       <c r="M150" s="4" t="n"/>
       <c r="N150" s="4" t="n"/>
+      <c r="O150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -20420,7 +20422,6 @@
       <c r="B151" s="3" t="n">
         <v>142.5</v>
       </c>
-      <c r="C151" s="4" t="n"/>
       <c r="D151" s="4" t="n"/>
       <c r="E151" s="4" t="n"/>
       <c r="F151" s="4" t="n"/>
@@ -20432,6 +20433,7 @@
       <c r="L151" s="4" t="n"/>
       <c r="M151" s="4" t="n"/>
       <c r="N151" s="4" t="n"/>
+      <c r="O151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -20440,7 +20442,6 @@
       <c r="B152" s="3" t="n">
         <v>142.5</v>
       </c>
-      <c r="C152" s="4" t="n"/>
       <c r="D152" s="4" t="n"/>
       <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="n"/>
@@ -20452,6 +20453,7 @@
       <c r="L152" s="4" t="n"/>
       <c r="M152" s="4" t="n"/>
       <c r="N152" s="4" t="n"/>
+      <c r="O152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -20460,7 +20462,6 @@
       <c r="B153" s="3" t="n">
         <v>142.5</v>
       </c>
-      <c r="C153" s="4" t="n"/>
       <c r="D153" s="4" t="n"/>
       <c r="E153" s="4" t="n"/>
       <c r="F153" s="4" t="n"/>
@@ -20472,6 +20473,7 @@
       <c r="L153" s="4" t="n"/>
       <c r="M153" s="4" t="n"/>
       <c r="N153" s="4" t="n"/>
+      <c r="O153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -20480,7 +20482,6 @@
       <c r="B154" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="n"/>
       <c r="E154" s="4" t="n"/>
       <c r="F154" s="4" t="n"/>
@@ -20492,6 +20493,7 @@
       <c r="L154" s="4" t="n"/>
       <c r="M154" s="4" t="n"/>
       <c r="N154" s="4" t="n"/>
+      <c r="O154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -20500,7 +20502,6 @@
       <c r="B155" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C155" s="4" t="n"/>
       <c r="D155" s="4" t="n"/>
       <c r="E155" s="4" t="n"/>
       <c r="F155" s="4" t="n"/>
@@ -20512,6 +20513,7 @@
       <c r="L155" s="4" t="n"/>
       <c r="M155" s="4" t="n"/>
       <c r="N155" s="4" t="n"/>
+      <c r="O155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -20520,7 +20522,6 @@
       <c r="B156" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C156" s="4" t="n"/>
       <c r="D156" s="4" t="n"/>
       <c r="E156" s="4" t="n"/>
       <c r="F156" s="4" t="n"/>
@@ -20532,6 +20533,7 @@
       <c r="L156" s="4" t="n"/>
       <c r="M156" s="4" t="n"/>
       <c r="N156" s="4" t="n"/>
+      <c r="O156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -20540,7 +20542,6 @@
       <c r="B157" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C157" s="4" t="n"/>
       <c r="D157" s="4" t="n"/>
       <c r="E157" s="4" t="n"/>
       <c r="F157" s="4" t="n"/>
@@ -20552,6 +20553,7 @@
       <c r="L157" s="4" t="n"/>
       <c r="M157" s="4" t="n"/>
       <c r="N157" s="4" t="n"/>
+      <c r="O157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -20560,7 +20562,6 @@
       <c r="B158" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C158" s="4" t="n"/>
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="4" t="n"/>
       <c r="F158" s="4" t="n"/>
@@ -20572,6 +20573,7 @@
       <c r="L158" s="4" t="n"/>
       <c r="M158" s="4" t="n"/>
       <c r="N158" s="4" t="n"/>
+      <c r="O158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -20580,7 +20582,6 @@
       <c r="B159" s="3" t="n">
         <v>146.5</v>
       </c>
-      <c r="C159" s="4" t="n"/>
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="4" t="n"/>
       <c r="F159" s="4" t="n"/>
@@ -20592,6 +20593,7 @@
       <c r="L159" s="4" t="n"/>
       <c r="M159" s="4" t="n"/>
       <c r="N159" s="4" t="n"/>
+      <c r="O159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -20600,7 +20602,6 @@
       <c r="B160" s="3" t="n">
         <v>147.5</v>
       </c>
-      <c r="C160" s="4" t="n"/>
       <c r="D160" s="4" t="n"/>
       <c r="E160" s="4" t="n"/>
       <c r="F160" s="4" t="n"/>
@@ -20612,6 +20613,7 @@
       <c r="L160" s="4" t="n"/>
       <c r="M160" s="4" t="n"/>
       <c r="N160" s="4" t="n"/>
+      <c r="O160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -20620,7 +20622,6 @@
       <c r="B161" s="3" t="n">
         <v>148.5</v>
       </c>
-      <c r="C161" s="4" t="n"/>
       <c r="D161" s="4" t="n"/>
       <c r="E161" s="4" t="n"/>
       <c r="F161" s="4" t="n"/>
@@ -20632,6 +20633,7 @@
       <c r="L161" s="4" t="n"/>
       <c r="M161" s="4" t="n"/>
       <c r="N161" s="4" t="n"/>
+      <c r="O161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
@@ -20640,7 +20642,6 @@
       <c r="B162" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C162" s="4" t="n"/>
       <c r="D162" s="4" t="n"/>
       <c r="E162" s="4" t="n"/>
       <c r="F162" s="4" t="n"/>
@@ -20652,6 +20653,7 @@
       <c r="L162" s="4" t="n"/>
       <c r="M162" s="4" t="n"/>
       <c r="N162" s="4" t="n"/>
+      <c r="O162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
@@ -20660,7 +20662,6 @@
       <c r="B163" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C163" s="4" t="n"/>
       <c r="D163" s="4" t="n"/>
       <c r="E163" s="4" t="n"/>
       <c r="F163" s="4" t="n"/>
@@ -20672,6 +20673,7 @@
       <c r="L163" s="4" t="n"/>
       <c r="M163" s="4" t="n"/>
       <c r="N163" s="4" t="n"/>
+      <c r="O163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
@@ -20680,7 +20682,6 @@
       <c r="B164" s="3" t="n">
         <v>141.5</v>
       </c>
-      <c r="C164" s="4" t="n"/>
       <c r="D164" s="4" t="n"/>
       <c r="E164" s="4" t="n"/>
       <c r="F164" s="4" t="n"/>
@@ -20692,6 +20693,7 @@
       <c r="L164" s="4" t="n"/>
       <c r="M164" s="4" t="n"/>
       <c r="N164" s="4" t="n"/>
+      <c r="O164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
@@ -20700,7 +20702,6 @@
       <c r="B165" s="3" t="n">
         <v>149.5</v>
       </c>
-      <c r="C165" s="4" t="n"/>
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="4" t="n"/>
       <c r="F165" s="4" t="n"/>
@@ -20712,6 +20713,7 @@
       <c r="L165" s="4" t="n"/>
       <c r="M165" s="4" t="n"/>
       <c r="N165" s="4" t="n"/>
+      <c r="O165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
@@ -20720,7 +20722,6 @@
       <c r="B166" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C166" s="4" t="n"/>
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="4" t="n"/>
       <c r="F166" s="4" t="n"/>
@@ -20732,6 +20733,7 @@
       <c r="L166" s="4" t="n"/>
       <c r="M166" s="4" t="n"/>
       <c r="N166" s="4" t="n"/>
+      <c r="O166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
@@ -20740,7 +20742,6 @@
       <c r="B167" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C167" s="4" t="n"/>
       <c r="D167" s="4" t="n"/>
       <c r="E167" s="4" t="n"/>
       <c r="F167" s="4" t="n"/>
@@ -20752,6 +20753,7 @@
       <c r="L167" s="4" t="n"/>
       <c r="M167" s="4" t="n"/>
       <c r="N167" s="4" t="n"/>
+      <c r="O167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
@@ -20760,7 +20762,6 @@
       <c r="B168" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="C168" s="4" t="n"/>
       <c r="D168" s="4" t="n"/>
       <c r="E168" s="4" t="n"/>
       <c r="F168" s="4" t="n"/>
@@ -20772,6 +20773,7 @@
       <c r="L168" s="4" t="n"/>
       <c r="M168" s="4" t="n"/>
       <c r="N168" s="4" t="n"/>
+      <c r="O168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
@@ -20780,7 +20782,6 @@
       <c r="B169" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C169" s="4" t="n"/>
       <c r="D169" s="4" t="n"/>
       <c r="E169" s="4" t="n"/>
       <c r="F169" s="4" t="n"/>
@@ -20792,6 +20793,7 @@
       <c r="L169" s="4" t="n"/>
       <c r="M169" s="4" t="n"/>
       <c r="N169" s="4" t="n"/>
+      <c r="O169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
@@ -20800,7 +20802,6 @@
       <c r="B170" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C170" s="4" t="n"/>
       <c r="D170" s="4" t="n"/>
       <c r="E170" s="4" t="n"/>
       <c r="F170" s="4" t="n"/>
@@ -20812,6 +20813,7 @@
       <c r="L170" s="4" t="n"/>
       <c r="M170" s="4" t="n"/>
       <c r="N170" s="4" t="n"/>
+      <c r="O170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
@@ -20820,7 +20822,6 @@
       <c r="B171" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C171" s="4" t="n"/>
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="4" t="n"/>
       <c r="F171" s="4" t="n"/>
@@ -20832,6 +20833,7 @@
       <c r="L171" s="4" t="n"/>
       <c r="M171" s="4" t="n"/>
       <c r="N171" s="4" t="n"/>
+      <c r="O171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
@@ -20840,7 +20842,6 @@
       <c r="B172" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C172" s="4" t="n"/>
       <c r="D172" s="4" t="n"/>
       <c r="E172" s="4" t="n"/>
       <c r="F172" s="4" t="n"/>
@@ -20852,6 +20853,7 @@
       <c r="L172" s="4" t="n"/>
       <c r="M172" s="4" t="n"/>
       <c r="N172" s="4" t="n"/>
+      <c r="O172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
@@ -20860,7 +20862,6 @@
       <c r="B173" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C173" s="4" t="n"/>
       <c r="D173" s="4" t="n"/>
       <c r="E173" s="4" t="n"/>
       <c r="F173" s="4" t="n"/>
@@ -20872,6 +20873,7 @@
       <c r="L173" s="4" t="n"/>
       <c r="M173" s="4" t="n"/>
       <c r="N173" s="4" t="n"/>
+      <c r="O173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
@@ -20880,7 +20882,6 @@
       <c r="B174" s="3" t="n">
         <v>144.5</v>
       </c>
-      <c r="C174" s="4" t="n"/>
       <c r="D174" s="4" t="n"/>
       <c r="E174" s="4" t="n"/>
       <c r="F174" s="4" t="n"/>
@@ -20892,6 +20893,7 @@
       <c r="L174" s="4" t="n"/>
       <c r="M174" s="4" t="n"/>
       <c r="N174" s="4" t="n"/>
+      <c r="O174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
@@ -20900,7 +20902,6 @@
       <c r="B175" s="3" t="n">
         <v>144.5</v>
       </c>
-      <c r="C175" s="4" t="n"/>
       <c r="D175" s="4" t="n"/>
       <c r="E175" s="4" t="n"/>
       <c r="F175" s="4" t="n"/>
@@ -20912,6 +20913,7 @@
       <c r="L175" s="4" t="n"/>
       <c r="M175" s="4" t="n"/>
       <c r="N175" s="4" t="n"/>
+      <c r="O175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
@@ -20920,7 +20922,6 @@
       <c r="B176" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C176" s="4" t="n"/>
       <c r="D176" s="4" t="n"/>
       <c r="E176" s="4" t="n"/>
       <c r="F176" s="4" t="n"/>
@@ -20932,6 +20933,7 @@
       <c r="L176" s="4" t="n"/>
       <c r="M176" s="4" t="n"/>
       <c r="N176" s="4" t="n"/>
+      <c r="O176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
@@ -20940,7 +20942,6 @@
       <c r="B177" s="3" t="n">
         <v>148.5</v>
       </c>
-      <c r="C177" s="4" t="n"/>
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="4" t="n"/>
       <c r="F177" s="4" t="n"/>
@@ -20952,6 +20953,7 @@
       <c r="L177" s="4" t="n"/>
       <c r="M177" s="4" t="n"/>
       <c r="N177" s="4" t="n"/>
+      <c r="O177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
@@ -20960,7 +20962,6 @@
       <c r="B178" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C178" s="4" t="n"/>
       <c r="D178" s="4" t="n"/>
       <c r="E178" s="4" t="n"/>
       <c r="F178" s="4" t="n"/>
@@ -20972,6 +20973,7 @@
       <c r="L178" s="4" t="n"/>
       <c r="M178" s="4" t="n"/>
       <c r="N178" s="4" t="n"/>
+      <c r="O178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
@@ -20980,7 +20982,6 @@
       <c r="B179" s="3" t="n">
         <v>146.5</v>
       </c>
-      <c r="C179" s="4" t="n"/>
       <c r="D179" s="4" t="n"/>
       <c r="E179" s="4" t="n"/>
       <c r="F179" s="4" t="n"/>
@@ -20992,6 +20993,7 @@
       <c r="L179" s="4" t="n"/>
       <c r="M179" s="4" t="n"/>
       <c r="N179" s="4" t="n"/>
+      <c r="O179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
@@ -21000,7 +21002,6 @@
       <c r="B180" s="3" t="n">
         <v>145.5</v>
       </c>
-      <c r="C180" s="4" t="n"/>
       <c r="D180" s="4" t="n"/>
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="4" t="n"/>
@@ -21012,6 +21013,7 @@
       <c r="L180" s="4" t="n"/>
       <c r="M180" s="4" t="n"/>
       <c r="N180" s="4" t="n"/>
+      <c r="O180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
@@ -21020,7 +21022,6 @@
       <c r="B181" s="3" t="n">
         <v>145.5</v>
       </c>
-      <c r="C181" s="4" t="n"/>
       <c r="D181" s="4" t="n"/>
       <c r="E181" s="4" t="n"/>
       <c r="F181" s="4" t="n"/>
@@ -21032,6 +21033,7 @@
       <c r="L181" s="4" t="n"/>
       <c r="M181" s="4" t="n"/>
       <c r="N181" s="4" t="n"/>
+      <c r="O181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
@@ -21040,7 +21042,6 @@
       <c r="B182" s="3" t="n">
         <v>143.5</v>
       </c>
-      <c r="C182" s="4" t="n"/>
       <c r="D182" s="4" t="n"/>
       <c r="E182" s="4" t="n"/>
       <c r="F182" s="4" t="n"/>
@@ -21052,6 +21053,7 @@
       <c r="L182" s="4" t="n"/>
       <c r="M182" s="4" t="n"/>
       <c r="N182" s="4" t="n"/>
+      <c r="O182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
@@ -21060,7 +21062,6 @@
       <c r="B183" s="3" t="n">
         <v>145.5</v>
       </c>
-      <c r="C183" s="4" t="n"/>
       <c r="D183" s="4" t="n"/>
       <c r="E183" s="4" t="n"/>
       <c r="F183" s="4" t="n"/>
@@ -21072,6 +21073,7 @@
       <c r="L183" s="4" t="n"/>
       <c r="M183" s="4" t="n"/>
       <c r="N183" s="4" t="n"/>
+      <c r="O183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
@@ -21080,7 +21082,6 @@
       <c r="B184" s="3" t="n">
         <v>140.5</v>
       </c>
-      <c r="C184" s="4" t="n"/>
       <c r="D184" s="4" t="n"/>
       <c r="E184" s="4" t="n"/>
       <c r="F184" s="4" t="n"/>
@@ -21092,6 +21093,7 @@
       <c r="L184" s="4" t="n"/>
       <c r="M184" s="4" t="n"/>
       <c r="N184" s="4" t="n"/>
+      <c r="O184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
@@ -21100,7 +21102,6 @@
       <c r="B185" s="3" t="n">
         <v>139.5</v>
       </c>
-      <c r="C185" s="4" t="n"/>
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="4" t="n"/>
       <c r="F185" s="4" t="n"/>
@@ -21112,6 +21113,7 @@
       <c r="L185" s="4" t="n"/>
       <c r="M185" s="4" t="n"/>
       <c r="N185" s="4" t="n"/>
+      <c r="O185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
@@ -21120,7 +21122,6 @@
       <c r="B186" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C186" s="4" t="n"/>
       <c r="D186" s="4" t="n"/>
       <c r="E186" s="4" t="n"/>
       <c r="F186" s="4" t="n"/>
@@ -21132,6 +21133,7 @@
       <c r="L186" s="4" t="n"/>
       <c r="M186" s="4" t="n"/>
       <c r="N186" s="4" t="n"/>
+      <c r="O186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
@@ -21140,7 +21142,6 @@
       <c r="B187" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C187" s="4" t="n"/>
       <c r="D187" s="4" t="n"/>
       <c r="E187" s="4" t="n"/>
       <c r="F187" s="4" t="n"/>
@@ -21152,6 +21153,7 @@
       <c r="L187" s="4" t="n"/>
       <c r="M187" s="4" t="n"/>
       <c r="N187" s="4" t="n"/>
+      <c r="O187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
@@ -21160,7 +21162,6 @@
       <c r="B188" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C188" s="4" t="n"/>
       <c r="D188" s="4" t="n"/>
       <c r="E188" s="4" t="n"/>
       <c r="F188" s="4" t="n"/>
@@ -21172,6 +21173,7 @@
       <c r="L188" s="4" t="n"/>
       <c r="M188" s="4" t="n"/>
       <c r="N188" s="4" t="n"/>
+      <c r="O188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
@@ -21180,7 +21182,6 @@
       <c r="B189" s="3" t="n">
         <v>129.5</v>
       </c>
-      <c r="C189" s="4" t="n"/>
       <c r="D189" s="4" t="n"/>
       <c r="E189" s="4" t="n"/>
       <c r="F189" s="4" t="n"/>
@@ -21192,6 +21193,7 @@
       <c r="L189" s="4" t="n"/>
       <c r="M189" s="4" t="n"/>
       <c r="N189" s="4" t="n"/>
+      <c r="O189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
@@ -21200,7 +21202,6 @@
       <c r="B190" s="3" t="n">
         <v>129.5</v>
       </c>
-      <c r="C190" s="4" t="n"/>
       <c r="D190" s="4" t="n"/>
       <c r="E190" s="4" t="n"/>
       <c r="F190" s="4" t="n"/>
@@ -21212,6 +21213,7 @@
       <c r="L190" s="4" t="n"/>
       <c r="M190" s="4" t="n"/>
       <c r="N190" s="4" t="n"/>
+      <c r="O190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
@@ -21220,7 +21222,6 @@
       <c r="B191" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C191" s="4" t="n"/>
       <c r="D191" s="4" t="n"/>
       <c r="E191" s="4" t="n"/>
       <c r="F191" s="4" t="n"/>
@@ -21232,6 +21233,7 @@
       <c r="L191" s="4" t="n"/>
       <c r="M191" s="4" t="n"/>
       <c r="N191" s="4" t="n"/>
+      <c r="O191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
@@ -21240,7 +21242,6 @@
       <c r="B192" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C192" s="4" t="n"/>
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="4" t="n"/>
       <c r="F192" s="4" t="n"/>
@@ -21252,6 +21253,7 @@
       <c r="L192" s="4" t="n"/>
       <c r="M192" s="4" t="n"/>
       <c r="N192" s="4" t="n"/>
+      <c r="O192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
@@ -21260,7 +21262,6 @@
       <c r="B193" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C193" s="4" t="n"/>
       <c r="D193" s="4" t="n"/>
       <c r="E193" s="4" t="n"/>
       <c r="F193" s="4" t="n"/>
@@ -21272,6 +21273,7 @@
       <c r="L193" s="4" t="n"/>
       <c r="M193" s="4" t="n"/>
       <c r="N193" s="4" t="n"/>
+      <c r="O193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
@@ -21280,7 +21282,6 @@
       <c r="B194" s="3" t="n">
         <v>133.5</v>
       </c>
-      <c r="C194" s="4" t="n"/>
       <c r="D194" s="4" t="n"/>
       <c r="E194" s="4" t="n"/>
       <c r="F194" s="4" t="n"/>
@@ -21292,6 +21293,7 @@
       <c r="L194" s="4" t="n"/>
       <c r="M194" s="4" t="n"/>
       <c r="N194" s="4" t="n"/>
+      <c r="O194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
@@ -21300,7 +21302,6 @@
       <c r="B195" s="3" t="n">
         <v>134.5</v>
       </c>
-      <c r="C195" s="4" t="n"/>
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="4" t="n"/>
       <c r="F195" s="4" t="n"/>
@@ -21312,6 +21313,7 @@
       <c r="L195" s="4" t="n"/>
       <c r="M195" s="4" t="n"/>
       <c r="N195" s="4" t="n"/>
+      <c r="O195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
@@ -21320,7 +21322,6 @@
       <c r="B196" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C196" s="4" t="n"/>
       <c r="D196" s="4" t="n"/>
       <c r="E196" s="4" t="n"/>
       <c r="F196" s="4" t="n"/>
@@ -21332,6 +21333,7 @@
       <c r="L196" s="4" t="n"/>
       <c r="M196" s="4" t="n"/>
       <c r="N196" s="4" t="n"/>
+      <c r="O196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
@@ -21340,7 +21342,6 @@
       <c r="B197" s="3" t="n">
         <v>139.5</v>
       </c>
-      <c r="C197" s="4" t="n"/>
       <c r="D197" s="4" t="n"/>
       <c r="E197" s="4" t="n"/>
       <c r="F197" s="4" t="n"/>
@@ -21352,6 +21353,7 @@
       <c r="L197" s="4" t="n"/>
       <c r="M197" s="4" t="n"/>
       <c r="N197" s="4" t="n"/>
+      <c r="O197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
@@ -21360,7 +21362,6 @@
       <c r="B198" s="3" t="n">
         <v>139.5</v>
       </c>
-      <c r="C198" s="4" t="n"/>
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="4" t="n"/>
       <c r="F198" s="4" t="n"/>
@@ -21372,6 +21373,7 @@
       <c r="L198" s="4" t="n"/>
       <c r="M198" s="4" t="n"/>
       <c r="N198" s="4" t="n"/>
+      <c r="O198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
@@ -21380,7 +21382,6 @@
       <c r="B199" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C199" s="4" t="n"/>
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="4" t="n"/>
       <c r="F199" s="4" t="n"/>
@@ -21392,6 +21393,7 @@
       <c r="L199" s="4" t="n"/>
       <c r="M199" s="4" t="n"/>
       <c r="N199" s="4" t="n"/>
+      <c r="O199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
@@ -21400,7 +21402,6 @@
       <c r="B200" s="3" t="n">
         <v>137.5</v>
       </c>
-      <c r="C200" s="4" t="n"/>
       <c r="D200" s="4" t="n"/>
       <c r="E200" s="4" t="n"/>
       <c r="F200" s="4" t="n"/>
@@ -21412,6 +21413,7 @@
       <c r="L200" s="4" t="n"/>
       <c r="M200" s="4" t="n"/>
       <c r="N200" s="4" t="n"/>
+      <c r="O200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
@@ -21420,7 +21422,6 @@
       <c r="B201" s="3" t="n">
         <v>142.5</v>
       </c>
-      <c r="C201" s="4" t="n"/>
       <c r="D201" s="4" t="n"/>
       <c r="E201" s="4" t="n"/>
       <c r="F201" s="4" t="n"/>
@@ -21432,6 +21433,7 @@
       <c r="L201" s="4" t="n"/>
       <c r="M201" s="4" t="n"/>
       <c r="N201" s="4" t="n"/>
+      <c r="O201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
@@ -21440,7 +21442,6 @@
       <c r="B202" s="3" t="n">
         <v>147.5</v>
       </c>
-      <c r="C202" s="4" t="n"/>
       <c r="D202" s="4" t="n"/>
       <c r="E202" s="4" t="n"/>
       <c r="F202" s="4" t="n"/>
@@ -21452,6 +21453,15 @@
       <c r="L202" s="4" t="n"/>
       <c r="M202" s="4" t="n"/>
       <c r="N202" s="4" t="n"/>
+      <c r="O202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B203" t="n">
+        <v>165</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/玉米大豆历史数据/玉米基差/Oregon Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Oregon Basis.xlsx
@@ -17339,7 +17339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O203"/>
+  <dimension ref="A1:O204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21463,6 +21463,14 @@
         <v>165</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B204" t="n">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
